--- a/examples/call_option_inputs.xlsx
+++ b/examples/call_option_inputs.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Market" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Curve" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="NettingSets" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trades" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="NettingSets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Trades" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,6 +543,18 @@
       </c>
       <c r="B11" t="n">
         <v>201</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reporting_ccy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -555,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,6 +602,11 @@
           <t>bbg_ticker</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ccy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -611,6 +629,11 @@
         <v>0.25757</v>
       </c>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -623,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,6 +660,11 @@
           <t>zero_rate</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ccy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -647,6 +675,11 @@
       <c r="B2" t="n">
         <v>0.0225</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -657,6 +690,11 @@
       <c r="B3" t="n">
         <v>0.0225</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -667,6 +705,11 @@
       <c r="B4" t="n">
         <v>0.0225</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -676,6 +719,71 @@
       </c>
       <c r="B5" t="n">
         <v>0.0228</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -689,107 +797,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>netting_set</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>counterparty</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>collateralized</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>threshold_cp</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>threshold_bank</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>mta</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ia_received</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ia_posted</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ia_posted_segregated</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>mpor_days</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>rounding</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NS_CP</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1000000000000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -803,6 +833,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>netting_set</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>counterparty</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>collateralized</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>threshold_cp</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>threshold_bank</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ia_received</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ia_posted</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ia_posted_segregated</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mpor_days</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rounding</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>csa_ccy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NS_CP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1000000000000000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
